--- a/data/DB2_Post_Analysis.xlsx
+++ b/data/DB2_Post_Analysis.xlsx
@@ -794,7 +794,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>47</v>
       </c>
@@ -896,7 +895,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>468</v>
       </c>
@@ -999,7 +997,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>686</v>
       </c>

--- a/data/DB2_Post_Analysis.xlsx
+++ b/data/DB2_Post_Analysis.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1038,6 +1038,1007 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A breakthrough in sleeping sickness treatment where a new single-dose medication (acoziborole) replaces dangerous arsenic-based drugs, made possible through pharmaceutical innovation and philanthropic commitment.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Moderately Relevant</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>It'sÂ hard to overstate how amazing this news is. When left untreated, sleeping sickness is a death sentenceâbut for years, the cure wasÂ nearly asÂ dangerous as the disease itself: an arsenic-based drug that killed 1 in 20 patients.â
+â
+That changed in 2018 with fexinidazole, an incredible, sa</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Bold Statement</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Inspirational</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2288</v>
+      </c>
+      <c r="O6" t="n">
+        <v>482</v>
+      </c>
+      <c r="P6" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Impact-driven healthcare innovation and global health breakthroughs are consistently popular on LinkedIn, particularly among founders focused on social impact and enterprise leaders. This specific intersection of pharmaceutical innovation and philanthropic distribution has moderate trending appeal.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Posts about major healthcare breakthroughs and philanthropic initiatives appear regularly but not excessively in professional networks, typically gaining significant engagement when shared by recognized thought leaders.</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7436474391065985024</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>This post works effectively by opening with an emotionally resonant bold statement ('hard to overstate how amazing') that immediately establishes stakes, followed by concrete contrasts (arsenic-based drug with 1-in-20 mortality vs. new safe single-dose pill) that make the impact tangible and dramatic. The structure moves logically from problem to solution to implementation, creating a clear narrative arc. However, the post has notable weaknesses: it reads more like a press release than authentic personal insight, contains formatting issues (Â symbols), and while inspiring, it lacks the specific founder/builder perspective that typically drives engagement in startup communities. For maximum impact with startup/VC audiences, the creator could emphasize learnings about bringing innovations to market, the challenges of global health distribution, or the strategic thinking behind partnerships like Gates Foundation collaboration rather than simply celebrating the outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Long Text + Image</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Social Impact</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>m-mama, an African maternal health emergency transport service, uses community drivers and alternative vehicles to get pregnant women to hospitals in time during childbirth crises, having saved over 5,000 lives since 2013.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Moderately Relevant</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>In many parts of sub-Saharan Africa, the biggest danger during childbirthâ¯isÂ thatÂ aÂ pregnantÂ woman in crisisÂ wonâtÂ make it to the hospital on time.Â â
+â
+That'sâ¯where m-mama comes in,Â usingÂ community driversâin cars and on bikes, boats, and even horsesâto getÂ those womenÂ the t</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Statistic</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Inspirational</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4138</v>
+      </c>
+      <c r="O7" t="n">
+        <v>670</v>
+      </c>
+      <c r="P7" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Impact-driven healthcare solutions in emerging markets are increasingly popular in the startup and VC community, with significant investor interest in solving maternal mortality in Africa.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Creators in the impact and healthcare space post about maternal health and transportation solutions moderately frequently, though this specific geographic focus is less common.</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7436225931213533184</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>This post works effectively by leading with a stark, relatable problem statement that immediately establishes stakes and emotional urgency—the danger of childbirth without timely hospital access resonates universally. The hook transitions smoothly into a concrete solution with impressive social proof (125,000+ emergencies responded to, 5,266+ lives saved), which builds credibility and demonstrates scale. The post maintains emotional resonance throughout by emphasizing the life-or-death nature of timing, creating a powerful narrative arc. However, the post could be strengthened by clarifying the organization's model (funding, sustainability, expansion plans) and including a stronger call-to-action that invites founder/investor engagement rather than passive admiration. The writing is clear and accessible, making it highly shareable, though it reads more as organizational storytelling than the strategic insights or tactical lessons that typically drive deeper engagement in founder and VC circles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Long Text</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TerraPower receives NRC approval to build an advanced nuclear reactor in Wyoming, marking the first commercial-scale advanced reactor construction permit. The project represents a significant milestone in clean energy infrastructure and job creation.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Moderately Relevant</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The NRC has approved the construction of TerraPower's advanced nuclear reactor inÂ Kemmerer, Wyoming.Â This is a huge milestoneâthe first construction permit for a commercial-scale advanced reactor.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Bold Statement</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Inspirational</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>3112</v>
+      </c>
+      <c r="O8" t="n">
+        <v>440</v>
+      </c>
+      <c r="P8" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Nuclear energy and climate tech are gaining momentum in startup/VC circles as investors seek scalable clean energy solutions. Advanced reactor companies are receiving significant venture and government backing, making this a trending sector.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Posts about regulatory approvals and infrastructure milestones in deep tech/climate are shared regularly but not as frequently as consumer tech or AI updates.</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7435849334618931200</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>This post succeeds in announcing a significant regulatory milestone with clear, concrete benefits (345 MW capacity, job creation, carbon-free energy), which appeals to impact-focused founders and climate VCs. However, the hook lacks punch—opening with a regulatory approval is factually important but emotionally neutral; a stronger opening might emphasize the breakthrough nature ("first of its kind") or the broader implications. The post is well-structured with tangible outcomes, but it reads more like a press release than a thought leadership piece that would drive viral engagement. The creator could improve shareability by connecting this to broader industry trends, investor thesis implications, or personal perspective on why this matters for the future of energy. While relevant to climate tech investors, it has limited appeal to general startup audiences, keeping shareability and engagement moderate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Long Text</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>m-mama's innovative emergency transport solution for pregnant women in rural Africa demonstrates how operational efficiency and community-based approaches can solve critical global health problems without requiring advanced technology.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Strongly Relevant</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>m-mama solvesâ¯one of global healthâsâ¯most persistentâ¯problems: getting pregnant women in crisis to the hospital in time.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Statistic</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Inspirational</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1825</v>
+      </c>
+      <c r="O9" t="n">
+        <v>270</v>
+      </c>
+      <c r="P9" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Impact-driven healthcare solutions and innovative approaches to global health problems are increasingly popular in startup and VC communities, particularly those focused on emerging markets and social impact investing.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Posts about impact-focused healthcare startups and innovative solutions to global health challenges appear regularly but remain compelling content in the startup/VC space, especially when backed by concrete metrics.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7435409048428019712</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>This post works effectively by leading with impressive quantitative impact (125,000+ emergencies, 5,266 lives saved) that immediately establishes credibility and scale. The hook is strong because the statistics are both surprising and emotionally resonant—demonstrating real human impact rather than abstract goals. The creator smartly pivots from the impressive numbers to a deeper insight: that breakthrough solutions don't always require cutting-edge technology, which challenges conventional wisdom and provides philosophical value. The 'sort of 911 for expectant mothers' analogy makes the concept instantly understandable to a global audience. However, the post could be strengthened by including a brief origin story or founder insight, and by clarifying the business model or funding status, which would increase relevance for the VC community. The structure is clean and easy to digest, making it highly shareable despite being a serious topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Long Text + Image</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A new anti-malarial drug represents a significant medical breakthrough after 25 years, demonstrating the power of scientific partnerships in addressing critical global health challenges.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moderately Relevant</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>This anti-malarial drugÂ is poised to becomeÂ the first breakthrough in malaria treatment in almost 25 years.Â This incredible step forward is a testament to partnership and scienceâand it couldnâtÂ have comeÂ at a more critical time.Â â</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Bold Statement</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Inspirational</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4214</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1003</v>
+      </c>
+      <c r="P10" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Biotech and healthtech innovation remain trending topics in startup/VC circles, though general malaria treatment may appeal more to impact investors and global health-focused funds than traditional tech VCs.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Healthcare and biotech breakthroughs are posted regularly in professional networks, but specific disease-treatment announcements are less frequent than general startup or fundraising content.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7423047848730103809</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>The post uses a strong bold statement hook that immediately communicates significance ('first breakthrough in almost 25 years'), which effectively captures attention and creates urgency. The emphasis on 'partnership and science' appeals to collaborative values that resonate with startup and VC communities. However, the post lacks specific details—no company name, funding amounts, timeline to market, or concrete impact metrics are provided, which limits its utility for investors evaluating the opportunity. The emotional appeal is present but somewhat generic; the post would be significantly strengthened by concrete examples, a personal connection to the problem, or details about the partnership structure. While the content is inspirational, it reads more like a press release than a distinctive LinkedIn perspective, reducing its shareability and engagement potential for the startup/VC audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Short Text</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fundraising</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Public acknowledgment and gratitude for philanthropic support toward polio eradication efforts from a major donor.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Slightly Relevant</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Thank you, HRH Alwaleed Bin Talal, for your continued leadershipÂ and commitmentÂ to polioÂ eradication,Â and for yourÂ generousÂ support through Alwaleed Philanthropies.â
+â
+TogetherÂ with partners around the world,Â we are ushering in a future whereÂ no childÂ hasÂ toÂ live inÂ fear of polio.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2124</v>
+      </c>
+      <c r="O11" t="n">
+        <v>204</v>
+      </c>
+      <c r="P11" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Philanthropic efforts and global health initiatives receive steady attention, but polio eradication specifically is a niche topic within the startup and VC community. This content appeals primarily to health-focused impact investors and NGO stakeholders rather than the broader startup ecosystem.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Public thank-you posts to major donors are relatively uncommon in the startup/VC space, with most impact-focused creators typically posting quarterly or less frequently about specific donor acknowledgments.</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7420148525314854913</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>This post falls short of effective engagement despite its positive intent. The hook—a simple thank-you statement—lacks compelling tension, curiosity, or emotional pull that would motivate shares or comments beyond the immediate network. The content reads as a formal acknowledgment rather than storytelling, offering little insight into impact metrics, personal connection, or forward-looking vision that would resonate with startup founders or VCs. While the mission is noble, the post provides minimal value-add beyond gratitude; it doesn't educate, inspire action, or present a contrarian perspective. To improve, the creator could quantify the impact achieved, share a specific beneficiary story, pose a challenge to other potential donors, or articulate a bold vision for what's next—transforming this from a transactional thank-you into content that inspires broader conversation and commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>How AI tools can augment healthcare delivery by supporting health workers to expand clinical capacity and improve care access in resource-constrained regions.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Moderately Relevant</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AI tools are a powerful way to support health workersâhelping them extend clinical capacity, improve quality of care, and reach more people, especially in places where resources are scarce.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Bold Statement</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Educational</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>6427</v>
+      </c>
+      <c r="O12" t="n">
+        <v>630</v>
+      </c>
+      <c r="P12" t="n">
+        <v>495</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>Above Average Engagement</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>AI in healthcare is consistently popular, but this specific angle on supporting health workers in resource-scarce areas is a niche subtopic that appeals primarily to healthcare-focused founders and impact investors rather than the broader startup/VC community.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Healthcare and AI professionals post about AI applications in clinical settings regularly, but this particular framing appears moderately frequently and doesn't represent a trending content style.</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7419886151131590656</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>This post lacks a compelling hook despite its socially important subject matter. The opening statement is declarative but not surprising or attention-grabbing—it reads more like a mission statement than a conversation starter. The post provides three benefits (extend capacity, improve quality, reach more people) but no specific examples, data, or stories that would make these claims concrete and memorable. For a LinkedIn audience of founders and VCs, the content needs either a surprising insight, a specific case study showing quantified impact, or a provocative question to generate discussion. The educational tone is appropriate but the execution is too generic; without evidence, specific use cases, or a clear call-to-action, the post feels more like promotional copy than thought leadership, which limits both engagement and shareability potential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Long Text</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>How AI tools are being deployed in African healthcare systems, specifically through a Gates Foundation and OpenAI initiative in Rwanda, to address clinician shortages and improve patient care access.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Moderately Relevant</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Despite cuts to aid over the past few years, Iâm optimistic about the future of health.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Bold Statement</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Inspirational</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2674</v>
+      </c>
+      <c r="O13" t="n">
+        <v>343</v>
+      </c>
+      <c r="P13" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>AI in healthcare and social impact is trending strongly in startup and VC circles, though this specific focus on African healthcare and public health infrastructure is more specialized than general AI adoption narratives.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Posts about AI solving healthcare challenges in emerging markets are moderately common but less frequent than general AI/tech posts, appearing roughly 2-3 times per month from major foundation and tech leaders.</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7419617889554599936</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>The post opens with an optimistic contrarian statement that works moderately well—pushing back against pessimism about aid cuts. However, the hook lacks specificity and personal stakes that would make it truly compelling; 'I'm optimistic' is somewhat generic for a LinkedIn opener. The content structure is solid, moving from problem identification (health worker shortages) to solution (AI tools) to concrete implementation (Rwanda pilot), which provides clarity and credibility. The value proposition is educational and mission-driven rather than commercially exciting, which limits appeal to typical VC audiences though it resonates with impact-focused investors. The post would be stronger with a concrete metric or outcome (e.g., 'early results show X% reduction in diagnostic time') and deeper personal narrative about why the creator believes in this approach. The association with Gates Foundation and OpenAI adds institutional weight but doesn't fully compensate for the somewhat abstract framing of the impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Long Text</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI's potential to address global challenges in agriculture, healthcare, and education, with emphasis on equitable access for underserved populations. The post argues that while AI will be transformative, deliberate effort is required to ensure benefits reach those who need it most.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Highly Relevant</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Of all the things humans have ever created, AI will change society the most. It will help solve many of our current problems while also bringing new challengesÂ very differentÂ from past innovations.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Bold Statement</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Inspirational</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2481</v>
+      </c>
+      <c r="O14" t="n">
+        <v>556</v>
+      </c>
+      <c r="P14" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>AI's societal impact is one of the most discussed topics in startup and VC circles right now, with particular momentum around AI applications in underserved markets and social impact. The emphasis on equitable distribution aligns with growing investor interest in impact-driven AI ventures.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>This specific angle—AI for social good and equitable access in emerging markets—is posted regularly by thought leaders and impact-focused VCs, appearing multiple times weekly across LinkedIn.</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7418916487928688641</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>This post works effectively by opening with a bold, attention-grabbing statement that immediately establishes stakes and scope, then systematically grounds the vision in three concrete, relatable domains (agriculture, healthcare, education) with specific pain points and AI solutions. The structure is clear and easy to follow, making complex ideas accessible while maintaining credibility through practical examples. However, the hook, while strong, is somewhat predictable in the AI discourse—many posts begin with 'AI will change society more than any innovation'—which slightly limits novelty. The post's greatest strength is its concluding insight about equitable outcomes requiring intentional effort, which elevates it beyond mere optimism and provides a call-to-action for builders and investors. To improve, the creator could have included a specific example, statistic, or company demonstrating these principles in action, which would add concrete proof points and increase memorability and engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Long Text</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The dramatic progress in HIV treatment and the potential to eliminate deaths through continued innovation and scaling, despite recent funding constraints.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Moderately Relevant</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>An HIV diagnosis used to be a death sentence, but thanks to revolutionary treatments, a person with HIV today can expect to liveÂ almost asÂ long as someone without the virus.Â With aÂ commitment to innovation and scaling these tools, deaths from this deadly disease could be virtually eliminated.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Inspirational</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2770</v>
+      </c>
+      <c r="O15" t="n">
+        <v>397</v>
+      </c>
+      <c r="P15" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>Average Engagement</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Healthcare innovation and public health challenges are consistently relevant in the startup/VC space, particularly around biotech and scaling solutions. Impact-focused healthcare topics trend well but are somewhat less dominant than fintech or AI topics.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Healthcare creators post about breakthrough treatments and disease elimination roughly 2-3 times weekly, with inspirational narratives being a common format.</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7418116754956095488</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>This post works effectively through a powerful contrasting hook that opens with historical context (death sentence) before pivoting to modern hope, creating emotional resonance that captures attention immediately. The structure moves logically from problem to solution to barrier to optimism, providing both intellectual and emotional satisfaction. However, the post's relevance to startup founders and VCs is somewhat indirect—while it speaks to impact and scaling, it lacks concrete actionable insights, specific funding mechanisms, or business model implications that would make it highly relevant to this audience. The creator could strengthen this significantly by explicitly connecting the narrative to venture opportunities, policy changes, or scalability frameworks that startup builders could act on. The inspirational tone and real-world impact story are strengths that drive shareability, but the post reads more like a social impact statement than a post with specific relevance to startup/VC economics and decision-making.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
